--- a/data/variants_processed.xlsx
+++ b/data/variants_processed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvesgreatti/github/Variant-Effects/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5DE4D8F1-9486-D248-A968-9EA9D4DE5A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{23E46056-31DA-6540-8C50-2E6607D129F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{DE238942-EE57-7647-A426-228E24414003}"/>
   </bookViews>
@@ -1227,6 +1227,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66C02CC-EA64-DD4D-BABB-23E744C1E58D}">
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
